--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2492"/>
+  <dimension ref="A1:E2493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67700,6 +67700,33 @@
         </is>
       </c>
     </row>
+    <row r="2493">
+      <c r="A2493" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2493" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2493" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D2493" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E2493" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2493"/>
+  <dimension ref="A1:E2494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67727,6 +67727,33 @@
         </is>
       </c>
     </row>
+    <row r="2494">
+      <c r="A2494" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B2494" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2494" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D2494" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E2494" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2494"/>
+  <dimension ref="A1:E2495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67754,6 +67754,33 @@
         </is>
       </c>
     </row>
+    <row r="2495">
+      <c r="A2495" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B2495" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2495" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D2495" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E2495" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2495"/>
+  <dimension ref="A1:E2496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67781,6 +67781,33 @@
         </is>
       </c>
     </row>
+    <row r="2496">
+      <c r="A2496" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B2496" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2496" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D2496" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E2496" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2496"/>
+  <dimension ref="A1:E2497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67808,6 +67808,33 @@
         </is>
       </c>
     </row>
+    <row r="2497">
+      <c r="A2497" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B2497" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2497" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D2497" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E2497" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2497"/>
+  <dimension ref="A1:E2498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67835,6 +67835,33 @@
         </is>
       </c>
     </row>
+    <row r="2498">
+      <c r="A2498" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B2498" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2498" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D2498" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E2498" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2498"/>
+  <dimension ref="A1:E2499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67862,6 +67862,33 @@
         </is>
       </c>
     </row>
+    <row r="2499">
+      <c r="A2499" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B2499" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2499" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D2499" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="E2499" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2499"/>
+  <dimension ref="A1:E2500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67889,6 +67889,33 @@
         </is>
       </c>
     </row>
+    <row r="2500">
+      <c r="A2500" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B2500" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2500" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D2500" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E2500" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2500"/>
+  <dimension ref="A1:E2501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67916,6 +67916,33 @@
         </is>
       </c>
     </row>
+    <row r="2501">
+      <c r="A2501" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B2501" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2501" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D2501" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E2501" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2501"/>
+  <dimension ref="A1:E2502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67943,6 +67943,33 @@
         </is>
       </c>
     </row>
+    <row r="2502">
+      <c r="A2502" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B2502" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2502" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D2502" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2502" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2502"/>
+  <dimension ref="A1:E2503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67970,6 +67970,33 @@
         </is>
       </c>
     </row>
+    <row r="2503">
+      <c r="A2503" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B2503" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2503" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D2503" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E2503" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2503"/>
+  <dimension ref="A1:E2504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67997,6 +67997,33 @@
         </is>
       </c>
     </row>
+    <row r="2504">
+      <c r="A2504" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B2504" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2504" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D2504" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E2504" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2504"/>
+  <dimension ref="A1:E2505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68024,6 +68024,33 @@
         </is>
       </c>
     </row>
+    <row r="2505">
+      <c r="A2505" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B2505" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2505" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D2505" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2505" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2505"/>
+  <dimension ref="A1:E2506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68051,6 +68051,33 @@
         </is>
       </c>
     </row>
+    <row r="2506">
+      <c r="A2506" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B2506" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2506" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D2506" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E2506" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2506"/>
+  <dimension ref="A1:E2507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68078,6 +68078,33 @@
         </is>
       </c>
     </row>
+    <row r="2507">
+      <c r="A2507" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B2507" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2507" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D2507" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E2507" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2507"/>
+  <dimension ref="A1:E2508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68105,6 +68105,33 @@
         </is>
       </c>
     </row>
+    <row r="2508">
+      <c r="A2508" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B2508" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2508" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D2508" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E2508" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2508"/>
+  <dimension ref="A1:E2509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68132,6 +68132,33 @@
         </is>
       </c>
     </row>
+    <row r="2509">
+      <c r="A2509" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B2509" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2509" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D2509" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E2509" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2509"/>
+  <dimension ref="A1:E2510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68159,6 +68159,33 @@
         </is>
       </c>
     </row>
+    <row r="2510">
+      <c r="A2510" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B2510" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2510" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D2510" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E2510" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2510"/>
+  <dimension ref="A1:E2511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68186,6 +68186,33 @@
         </is>
       </c>
     </row>
+    <row r="2511">
+      <c r="A2511" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B2511" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2511" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D2511" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E2511" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2511"/>
+  <dimension ref="A1:E2512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68213,6 +68213,33 @@
         </is>
       </c>
     </row>
+    <row r="2512">
+      <c r="A2512" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B2512" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2512" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D2512" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E2512" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2512"/>
+  <dimension ref="A1:E2513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68240,6 +68240,33 @@
         </is>
       </c>
     </row>
+    <row r="2513">
+      <c r="A2513" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2513" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2513" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D2513" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E2513" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2513"/>
+  <dimension ref="A1:E2514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68267,6 +68267,33 @@
         </is>
       </c>
     </row>
+    <row r="2514">
+      <c r="A2514" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B2514" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2514" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D2514" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E2514" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2514"/>
+  <dimension ref="A1:E2515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68294,6 +68294,33 @@
         </is>
       </c>
     </row>
+    <row r="2515">
+      <c r="A2515" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B2515" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2515" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D2515" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E2515" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2515"/>
+  <dimension ref="A1:E2516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68321,6 +68321,33 @@
         </is>
       </c>
     </row>
+    <row r="2516">
+      <c r="A2516" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B2516" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2516" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D2516" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E2516" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2516"/>
+  <dimension ref="A1:E2517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68348,6 +68348,33 @@
         </is>
       </c>
     </row>
+    <row r="2517">
+      <c r="A2517" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B2517" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2517" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D2517" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E2517" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2517"/>
+  <dimension ref="A1:E2518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68375,6 +68375,33 @@
         </is>
       </c>
     </row>
+    <row r="2518">
+      <c r="A2518" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B2518" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2518" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D2518" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E2518" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2518"/>
+  <dimension ref="A1:E2519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68402,6 +68402,33 @@
         </is>
       </c>
     </row>
+    <row r="2519">
+      <c r="A2519" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B2519" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2519" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D2519" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E2519" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2519"/>
+  <dimension ref="A1:E2520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68429,6 +68429,33 @@
         </is>
       </c>
     </row>
+    <row r="2520">
+      <c r="A2520" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B2520" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2520" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D2520" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E2520" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2520"/>
+  <dimension ref="A1:E2521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68456,6 +68456,33 @@
         </is>
       </c>
     </row>
+    <row r="2521">
+      <c r="A2521" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B2521" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2521" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D2521" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E2521" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2521"/>
+  <dimension ref="A1:E2522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68483,6 +68483,33 @@
         </is>
       </c>
     </row>
+    <row r="2522">
+      <c r="A2522" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B2522" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2522" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D2522" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E2522" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2522"/>
+  <dimension ref="A1:E2523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68510,6 +68510,33 @@
         </is>
       </c>
     </row>
+    <row r="2523">
+      <c r="A2523" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B2523" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2523" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D2523" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E2523" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2523"/>
+  <dimension ref="A1:E2524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68537,6 +68537,33 @@
         </is>
       </c>
     </row>
+    <row r="2524">
+      <c r="A2524" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B2524" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2524" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D2524" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E2524" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2524"/>
+  <dimension ref="A1:E2525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68564,6 +68564,33 @@
         </is>
       </c>
     </row>
+    <row r="2525">
+      <c r="A2525" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B2525" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2525" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D2525" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E2525" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2525"/>
+  <dimension ref="A1:E2526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68591,6 +68591,33 @@
         </is>
       </c>
     </row>
+    <row r="2526">
+      <c r="A2526" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B2526" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2526" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D2526" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E2526" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2526"/>
+  <dimension ref="A1:E2527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68618,6 +68618,33 @@
         </is>
       </c>
     </row>
+    <row r="2527">
+      <c r="A2527" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B2527" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2527" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D2527" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E2527" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2527"/>
+  <dimension ref="A1:E2528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68645,6 +68645,33 @@
         </is>
       </c>
     </row>
+    <row r="2528">
+      <c r="A2528" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B2528" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2528" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D2528" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E2528" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2528"/>
+  <dimension ref="A1:E2529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68672,6 +68672,33 @@
         </is>
       </c>
     </row>
+    <row r="2529">
+      <c r="A2529" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B2529" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2529" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D2529" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E2529" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2529"/>
+  <dimension ref="A1:E2530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68699,6 +68699,33 @@
         </is>
       </c>
     </row>
+    <row r="2530">
+      <c r="A2530" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B2530" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2530" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D2530" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E2530" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2530"/>
+  <dimension ref="A1:E2531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68726,6 +68726,33 @@
         </is>
       </c>
     </row>
+    <row r="2531">
+      <c r="A2531" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B2531" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2531" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D2531" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E2531" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2531"/>
+  <dimension ref="A1:E2532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68753,6 +68753,33 @@
         </is>
       </c>
     </row>
+    <row r="2532">
+      <c r="A2532" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B2532" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2532" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D2532" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E2532" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2532"/>
+  <dimension ref="A1:E2533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68780,6 +68780,33 @@
         </is>
       </c>
     </row>
+    <row r="2533">
+      <c r="A2533" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B2533" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2533" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D2533" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E2533" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2533"/>
+  <dimension ref="A1:E2534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68807,6 +68807,33 @@
         </is>
       </c>
     </row>
+    <row r="2534">
+      <c r="A2534" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B2534" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2534" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D2534" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E2534" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2534"/>
+  <dimension ref="A1:E2535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68834,6 +68834,33 @@
         </is>
       </c>
     </row>
+    <row r="2535">
+      <c r="A2535" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B2535" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2535" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D2535" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E2535" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2535"/>
+  <dimension ref="A1:E2536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68861,6 +68861,33 @@
         </is>
       </c>
     </row>
+    <row r="2536">
+      <c r="A2536" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B2536" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2536" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D2536" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E2536" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2536"/>
+  <dimension ref="A1:E2537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68888,6 +68888,33 @@
         </is>
       </c>
     </row>
+    <row r="2537">
+      <c r="A2537" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B2537" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2537" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D2537" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E2537" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2537"/>
+  <dimension ref="A1:E2538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68915,6 +68915,33 @@
         </is>
       </c>
     </row>
+    <row r="2538">
+      <c r="A2538" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B2538" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2538" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D2538" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E2538" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2538"/>
+  <dimension ref="A1:E2539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68942,6 +68942,33 @@
         </is>
       </c>
     </row>
+    <row r="2539">
+      <c r="A2539" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2539" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2539" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D2539" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E2539" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2539"/>
+  <dimension ref="A1:E2540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68969,6 +68969,33 @@
         </is>
       </c>
     </row>
+    <row r="2540">
+      <c r="A2540" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B2540" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2540" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D2540" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E2540" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2540"/>
+  <dimension ref="A1:E2541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68996,6 +68996,33 @@
         </is>
       </c>
     </row>
+    <row r="2541">
+      <c r="A2541" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2541" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2541" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D2541" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E2541" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2541"/>
+  <dimension ref="A1:E2542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69023,6 +69023,33 @@
         </is>
       </c>
     </row>
+    <row r="2542">
+      <c r="A2542" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2542" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2542" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D2542" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E2542" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2542"/>
+  <dimension ref="A1:E2543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69050,6 +69050,33 @@
         </is>
       </c>
     </row>
+    <row r="2543">
+      <c r="A2543" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2543" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2543" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D2543" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E2543" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2543"/>
+  <dimension ref="A1:E2544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69077,6 +69077,33 @@
         </is>
       </c>
     </row>
+    <row r="2544">
+      <c r="A2544" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2544" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2544" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D2544" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E2544" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2544"/>
+  <dimension ref="A1:E2545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69104,6 +69104,33 @@
         </is>
       </c>
     </row>
+    <row r="2545">
+      <c r="A2545" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2545" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2545" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D2545" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E2545" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2545"/>
+  <dimension ref="A1:E2546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69131,6 +69131,33 @@
         </is>
       </c>
     </row>
+    <row r="2546">
+      <c r="A2546" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B2546" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2546" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D2546" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E2546" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2546"/>
+  <dimension ref="A1:E2547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69158,6 +69158,33 @@
         </is>
       </c>
     </row>
+    <row r="2547">
+      <c r="A2547" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B2547" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2547" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D2547" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E2547" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2547"/>
+  <dimension ref="A1:E2548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69185,6 +69185,33 @@
         </is>
       </c>
     </row>
+    <row r="2548">
+      <c r="A2548" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2548" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2548" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D2548" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E2548" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2548"/>
+  <dimension ref="A1:E2549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69212,6 +69212,33 @@
         </is>
       </c>
     </row>
+    <row r="2549">
+      <c r="A2549" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2549" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2549" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D2549" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E2549" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2549"/>
+  <dimension ref="A1:E2550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69239,6 +69239,33 @@
         </is>
       </c>
     </row>
+    <row r="2550">
+      <c r="A2550" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B2550" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2550" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D2550" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E2550" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2550"/>
+  <dimension ref="A1:E2551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69266,6 +69266,33 @@
         </is>
       </c>
     </row>
+    <row r="2551">
+      <c r="A2551" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B2551" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2551" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D2551" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E2551" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2551"/>
+  <dimension ref="A1:E2552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69293,6 +69293,33 @@
         </is>
       </c>
     </row>
+    <row r="2552">
+      <c r="A2552" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B2552" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2552" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D2552" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E2552" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2552"/>
+  <dimension ref="A1:E2553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69320,6 +69320,33 @@
         </is>
       </c>
     </row>
+    <row r="2553">
+      <c r="A2553" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B2553" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2553" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D2553" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E2553" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2553"/>
+  <dimension ref="A1:E2554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69347,6 +69347,33 @@
         </is>
       </c>
     </row>
+    <row r="2554">
+      <c r="A2554" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B2554" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2554" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D2554" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E2554" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2554"/>
+  <dimension ref="A1:E2555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69374,6 +69374,33 @@
         </is>
       </c>
     </row>
+    <row r="2555">
+      <c r="A2555" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B2555" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2555" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D2555" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E2555" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2555"/>
+  <dimension ref="A1:E2556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69401,6 +69401,33 @@
         </is>
       </c>
     </row>
+    <row r="2556">
+      <c r="A2556" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B2556" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2556" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D2556" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E2556" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2556"/>
+  <dimension ref="A1:E2557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69428,6 +69428,33 @@
         </is>
       </c>
     </row>
+    <row r="2557">
+      <c r="A2557" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B2557" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2557" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D2557" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E2557" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2557"/>
+  <dimension ref="A1:E2558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69455,6 +69455,33 @@
         </is>
       </c>
     </row>
+    <row r="2558">
+      <c r="A2558" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B2558" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2558" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D2558" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E2558" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2558"/>
+  <dimension ref="A1:E2559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69482,6 +69482,33 @@
         </is>
       </c>
     </row>
+    <row r="2559">
+      <c r="A2559" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B2559" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2559" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D2559" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E2559" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2559"/>
+  <dimension ref="A1:E2560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69509,6 +69509,33 @@
         </is>
       </c>
     </row>
+    <row r="2560">
+      <c r="A2560" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B2560" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2560" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D2560" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E2560" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2560"/>
+  <dimension ref="A1:E2561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69536,6 +69536,33 @@
         </is>
       </c>
     </row>
+    <row r="2561">
+      <c r="A2561" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B2561" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2561" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D2561" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E2561" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2561"/>
+  <dimension ref="A1:E2562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69563,6 +69563,33 @@
         </is>
       </c>
     </row>
+    <row r="2562">
+      <c r="A2562" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B2562" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2562" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D2562" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E2562" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2562"/>
+  <dimension ref="A1:E2563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69590,6 +69590,33 @@
         </is>
       </c>
     </row>
+    <row r="2563">
+      <c r="A2563" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B2563" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2563" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D2563" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E2563" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2563"/>
+  <dimension ref="A1:E2564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69617,6 +69617,33 @@
         </is>
       </c>
     </row>
+    <row r="2564">
+      <c r="A2564" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2564" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2564" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D2564" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E2564" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2564"/>
+  <dimension ref="A1:E2565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69644,6 +69644,33 @@
         </is>
       </c>
     </row>
+    <row r="2565">
+      <c r="A2565" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B2565" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2565" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D2565" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="E2565" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2565"/>
+  <dimension ref="A1:E2566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69671,6 +69671,33 @@
         </is>
       </c>
     </row>
+    <row r="2566">
+      <c r="A2566" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B2566" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2566" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D2566" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E2566" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2566"/>
+  <dimension ref="A1:E2567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69698,6 +69698,33 @@
         </is>
       </c>
     </row>
+    <row r="2567">
+      <c r="A2567" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B2567" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2567" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D2567" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E2567" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2567"/>
+  <dimension ref="A1:E2568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69725,6 +69725,33 @@
         </is>
       </c>
     </row>
+    <row r="2568">
+      <c r="A2568" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B2568" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2568" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D2568" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E2568" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2568"/>
+  <dimension ref="A1:E2569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69752,6 +69752,33 @@
         </is>
       </c>
     </row>
+    <row r="2569">
+      <c r="A2569" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B2569" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2569" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D2569" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E2569" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2569"/>
+  <dimension ref="A1:E2570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69779,6 +69779,33 @@
         </is>
       </c>
     </row>
+    <row r="2570">
+      <c r="A2570" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B2570" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2570" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D2570" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E2570" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2570"/>
+  <dimension ref="A1:E2571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69806,6 +69806,33 @@
         </is>
       </c>
     </row>
+    <row r="2571">
+      <c r="A2571" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B2571" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2571" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D2571" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E2571" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2571"/>
+  <dimension ref="A1:E2572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69833,6 +69833,33 @@
         </is>
       </c>
     </row>
+    <row r="2572">
+      <c r="A2572" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B2572" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2572" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D2572" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E2572" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2572"/>
+  <dimension ref="A1:E2573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69860,6 +69860,33 @@
         </is>
       </c>
     </row>
+    <row r="2573">
+      <c r="A2573" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B2573" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2573" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D2573" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E2573" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2573"/>
+  <dimension ref="A1:E2574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69887,6 +69887,33 @@
         </is>
       </c>
     </row>
+    <row r="2574">
+      <c r="A2574" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B2574" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2574" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D2574" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E2574" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2574"/>
+  <dimension ref="A1:E2576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69914,6 +69914,60 @@
         </is>
       </c>
     </row>
+    <row r="2575">
+      <c r="A2575" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B2575" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2575" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D2575" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E2575" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="2576">
+      <c r="A2576" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B2576" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2576" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D2576" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E2576" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2576"/>
+  <dimension ref="A1:E2577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69968,6 +69968,33 @@
         </is>
       </c>
     </row>
+    <row r="2577">
+      <c r="A2577" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2577" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2577" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D2577" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E2577" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2577"/>
+  <dimension ref="A1:E2578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69995,6 +69995,33 @@
         </is>
       </c>
     </row>
+    <row r="2578">
+      <c r="A2578" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2578" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2578" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D2578" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E2578" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2578"/>
+  <dimension ref="A1:E2579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70022,6 +70022,33 @@
         </is>
       </c>
     </row>
+    <row r="2579">
+      <c r="A2579" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2579" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2579" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D2579" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E2579" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2579"/>
+  <dimension ref="A1:E2580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70049,6 +70049,33 @@
         </is>
       </c>
     </row>
+    <row r="2580">
+      <c r="A2580" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2580" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2580" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D2580" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E2580" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2580"/>
+  <dimension ref="A1:E2581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70076,6 +70076,33 @@
         </is>
       </c>
     </row>
+    <row r="2581">
+      <c r="A2581" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2581" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2581" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D2581" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E2581" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2581"/>
+  <dimension ref="A1:E2582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70103,6 +70103,33 @@
         </is>
       </c>
     </row>
+    <row r="2582">
+      <c r="A2582" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B2582" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2582" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D2582" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E2582" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
